--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE424CC-2518-4B98-8B1D-EEBEBC6DAC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED35BA5A-C0B1-4113-AA0C-36BEA9D69899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Reviewer" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$193</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1468">
   <si>
     <t>Reviewer Name</t>
   </si>
@@ -4614,6 +4614,39 @@
   </si>
   <si>
     <t>Reporting guidelines for plastic ingestion by wildlife.</t>
+  </si>
+  <si>
+    <t>A QA/QC screening framework to assess studies reporting micro plastic presence in human organs, tissues, and bodily fluids</t>
+  </si>
+  <si>
+    <t>Koelmans et al. 2026</t>
+  </si>
+  <si>
+    <t>10.1016/j.envint.2026.110429</t>
+  </si>
+  <si>
+    <t>Developed a QA/QC screening protocol with fourteen criteria across three categories: sampling methods, particle characterization, and contamination mitigation. We applied this tool to evaluate 133 datasets from 101 studies reporting measurements of microplastics in human organs, tissues, and bodily fluids</t>
+  </si>
+  <si>
+    <t>Guidance, checklist, critical review</t>
+  </si>
+  <si>
+    <t>Quality Assurance and −control (QA/QC) tools are essential to evaluate the reliability of data on nano- and microplastic particles measured in the human body for use in risk assessment. Currently, no such criteria exist for human samples. To support human health risk assessment related to internal exposure to these particles, we developed a QA/QC screening protocol with fourteen criteria across three categories: sampling methods, particle characterization, and contamination mitigation. We applied this tool to evaluate 133 datasets from 101 studies reporting measurements of microplastics in human organs, tissues, and bodily fluids. None of the studies nor datasets met all essential QA/QC criteria, indicating their current value lies primarily in pioneering exploratory research. Common gaps were found in sample representativeness, the use of positive controls, and documentation of blank procedures. Data were also sparse for organs critical to toxicokinetic processes and physiologically-based kinetic modelling, highlighting a significant knowledge gap. Even in studies with relatively strong QA/QC performance, some findings warrant careful evaluation of biological plausibility. We recommend that future studies not only improve QA/QC practices but also explicitly reflect on the plausibility of their results to avoid misinterpretation and miscommunication.</t>
+  </si>
+  <si>
+    <t>Microplastics standards in Australia and around the world: challenges and perspectives</t>
+  </si>
+  <si>
+    <t>Snigirova et al., 2026</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fenvs.2026.1835134</t>
+  </si>
+  <si>
+    <t>This study provides a review of existing microplastic-related standards. In total, 58 active standards were identified on Standards Australia International Global database. Their scope, spanning sampling, extraction, characterisation and reporting protocols, is reviewed in the context of practical applications. The review also evaluates the rollout of policy responses aiming to curb the burden of some of the main microplastics sources such as microbeads, tyre particles, textiles, and synthetic turf. Positive examples of regulations and initiatives are highlighted across multiple jurisdictions, illustrating the diversity of global approaches. The analysis reveals current gaps in microplastics standardisation and a lack of interlaboratory comparison studies, especially for airborne microplastics, nanoplastics, analysis in biological samples and reference materials. Uncertainties regarding environmental behaviour and degradation pathways of biodegradable polymers and their contribution to microplastics loads can further complicate guidelines’ introduction. Finally, the study discusses possible ways of integrating microplastics regulation within existing environmental protection legislation frameworks to introduce future microplastics standards.</t>
+  </si>
+  <si>
+    <t>Review of 58 active standards were identified on Standards Australia International Global database</t>
   </si>
 </sst>
 </file>
@@ -4808,7 +4841,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4937,8 +4970,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -5142,12 +5181,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5422,38 +5483,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5476,7 +5513,40 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5996,8 +6066,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB190" totalsRowShown="0" headerRowBorderDxfId="51">
-  <autoFilter ref="A2:BB190" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB193" totalsRowShown="0" headerRowBorderDxfId="51">
+  <autoFilter ref="A2:BB193" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BB176">
     <sortCondition ref="A2:A176"/>
   </sortState>
@@ -6394,75 +6464,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="102" t="s">
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="103"/>
+      <c r="O1" s="98"/>
       <c r="P1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="104" t="s">
+      <c r="Q1" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="98"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="105" t="s">
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="98"/>
+      <c r="AE1" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="106" t="s">
+      <c r="AF1" s="98"/>
+      <c r="AG1" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="AH1" s="98"/>
-      <c r="AI1" s="98"/>
-      <c r="AJ1" s="103"/>
+      <c r="AH1" s="97"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="98"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="AM1" s="78"/>
-      <c r="AN1" s="107" t="s">
+      <c r="AN1" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="AO1" s="103"/>
-      <c r="AP1" s="108" t="s">
+      <c r="AO1" s="98"/>
+      <c r="AP1" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="103"/>
-      <c r="AR1" s="109" t="s">
+      <c r="AQ1" s="98"/>
+      <c r="AR1" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="110"/>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
       <c r="AV1" s="17" t="s">
         <v>44</v>
       </c>
@@ -6471,11 +6541,11 @@
       </c>
       <c r="AX1" s="19"/>
       <c r="AY1" s="19"/>
-      <c r="AZ1" s="111" t="s">
+      <c r="AZ1" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="112"/>
-      <c r="BB1" s="113"/>
+      <c r="BA1" s="104"/>
+      <c r="BB1" s="105"/>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" ht="57.75" customHeight="1">
       <c r="A2" s="20" t="s">
@@ -24497,7 +24567,7 @@
       <c r="B190" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="C190" s="114">
+      <c r="C190" s="83">
         <v>2026</v>
       </c>
       <c r="D190" s="3" t="s">
@@ -24587,74 +24657,298 @@
       </c>
     </row>
     <row r="191" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A191" s="70"/>
-      <c r="AW191" s="10"/>
+      <c r="A191" s="70">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C191" s="115">
+        <v>2026</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E191" s="94" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F191" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G191" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="H191" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="I191" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="J191" s="81"/>
+      <c r="K191" s="42" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L191" s="83"/>
+      <c r="M191" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="N191" s="82"/>
+      <c r="O191" s="82"/>
+      <c r="P191" s="82"/>
+      <c r="Q191" s="82"/>
+      <c r="R191" s="82"/>
+      <c r="S191" s="82"/>
+      <c r="T191" s="82"/>
+      <c r="U191" s="82"/>
+      <c r="V191" s="82"/>
+      <c r="W191" s="82"/>
+      <c r="X191" s="82"/>
+      <c r="Y191" s="82"/>
+      <c r="Z191" s="82"/>
+      <c r="AA191" s="82">
+        <v>3</v>
+      </c>
+      <c r="AB191" s="82"/>
+      <c r="AC191" s="82"/>
+      <c r="AD191" s="82"/>
+      <c r="AE191" s="82">
+        <v>3</v>
+      </c>
+      <c r="AF191" s="82"/>
+      <c r="AG191" s="82"/>
+      <c r="AH191" s="82"/>
+      <c r="AI191" s="82"/>
+      <c r="AJ191" s="82"/>
+      <c r="AK191" s="82"/>
+      <c r="AL191" s="82"/>
+      <c r="AM191" s="82"/>
+      <c r="AN191" s="82">
+        <v>3</v>
+      </c>
+      <c r="AO191" s="67"/>
+      <c r="AP191" s="82"/>
+      <c r="AQ191" s="82"/>
+      <c r="AR191" s="82"/>
+      <c r="AS191" s="82"/>
+      <c r="AT191" s="67"/>
+      <c r="AU191" s="82"/>
+      <c r="AV191" s="82"/>
+      <c r="AW191" s="10" t="s">
+        <v>1460</v>
+      </c>
+      <c r="AX191" s="83"/>
+      <c r="AY191" s="83"/>
+      <c r="AZ191" s="10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BA191" s="45" t="s">
+        <v>1461</v>
+      </c>
+      <c r="BB191" s="10" t="s">
+        <v>1462</v>
+      </c>
     </row>
     <row r="192" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A192" s="70"/>
-      <c r="AW192" s="10"/>
-    </row>
-    <row r="193" spans="1:49" ht="14.3" customHeight="1">
+      <c r="A192" s="70">
+        <v>191</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C192" s="115">
+        <v>2026</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E192" s="89" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F192" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="G192" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="H192" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="I192" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="J192" s="81"/>
+      <c r="K192" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="L192" s="83"/>
+      <c r="M192" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="N192" s="82"/>
+      <c r="O192" s="82"/>
+      <c r="P192" s="82"/>
+      <c r="Q192" s="82"/>
+      <c r="R192" s="82"/>
+      <c r="S192" s="82"/>
+      <c r="T192" s="82"/>
+      <c r="U192" s="82"/>
+      <c r="V192" s="82"/>
+      <c r="W192" s="82"/>
+      <c r="X192" s="82"/>
+      <c r="Y192" s="82"/>
+      <c r="Z192" s="82"/>
+      <c r="AA192" s="82"/>
+      <c r="AB192" s="82"/>
+      <c r="AC192" s="82"/>
+      <c r="AD192" s="82"/>
+      <c r="AE192" s="82"/>
+      <c r="AF192" s="82"/>
+      <c r="AG192" s="82"/>
+      <c r="AH192" s="82"/>
+      <c r="AI192" s="82"/>
+      <c r="AJ192" s="82"/>
+      <c r="AK192" s="82"/>
+      <c r="AL192" s="82">
+        <v>3</v>
+      </c>
+      <c r="AM192" s="82"/>
+      <c r="AN192" s="82"/>
+      <c r="AO192" s="67"/>
+      <c r="AP192" s="82"/>
+      <c r="AQ192" s="82"/>
+      <c r="AR192" s="82"/>
+      <c r="AS192" s="82"/>
+      <c r="AT192" s="67"/>
+      <c r="AU192" s="82"/>
+      <c r="AV192" s="82"/>
+      <c r="AW192" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="AX192" s="83"/>
+      <c r="AY192" s="83"/>
+      <c r="AZ192" s="10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BA192" s="45" t="s">
+        <v>1467</v>
+      </c>
+      <c r="BB192" s="10" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="193" spans="1:54" ht="14.3" customHeight="1">
       <c r="A193" s="70"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="115"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="68"/>
+      <c r="G193" s="90"/>
+      <c r="H193" s="114"/>
+      <c r="I193" s="116"/>
+      <c r="J193" s="81"/>
+      <c r="K193" s="91"/>
+      <c r="L193" s="83"/>
+      <c r="M193" s="117"/>
+      <c r="N193" s="82"/>
+      <c r="O193" s="82"/>
+      <c r="P193" s="82"/>
+      <c r="Q193" s="82"/>
+      <c r="R193" s="82"/>
+      <c r="S193" s="82"/>
+      <c r="T193" s="82"/>
+      <c r="U193" s="82"/>
+      <c r="V193" s="82"/>
+      <c r="W193" s="82"/>
+      <c r="X193" s="82"/>
+      <c r="Y193" s="82"/>
+      <c r="Z193" s="82"/>
+      <c r="AA193" s="82"/>
+      <c r="AB193" s="82"/>
+      <c r="AC193" s="82"/>
+      <c r="AD193" s="82"/>
+      <c r="AE193" s="82"/>
+      <c r="AF193" s="82"/>
+      <c r="AG193" s="82"/>
+      <c r="AH193" s="82"/>
+      <c r="AI193" s="82"/>
+      <c r="AJ193" s="82"/>
+      <c r="AK193" s="82"/>
+      <c r="AL193" s="82"/>
+      <c r="AM193" s="82"/>
+      <c r="AN193" s="82"/>
+      <c r="AO193" s="67"/>
+      <c r="AP193" s="82"/>
+      <c r="AQ193" s="82"/>
+      <c r="AR193" s="82"/>
+      <c r="AS193" s="82"/>
+      <c r="AT193" s="67"/>
+      <c r="AU193" s="82"/>
+      <c r="AV193" s="82"/>
       <c r="AW193" s="10"/>
-    </row>
-    <row r="194" spans="1:49" ht="14.3" customHeight="1">
+      <c r="AX193" s="83"/>
+      <c r="AY193" s="83"/>
+      <c r="AZ193" s="10"/>
+      <c r="BA193" s="45"/>
+      <c r="BB193" s="10"/>
+    </row>
+    <row r="194" spans="1:54" ht="14.3" customHeight="1">
       <c r="A194" s="70"/>
       <c r="AW194" s="10"/>
     </row>
-    <row r="195" spans="1:49" ht="14.3" customHeight="1">
+    <row r="195" spans="1:54" ht="14.3" customHeight="1">
       <c r="A195" s="70"/>
       <c r="AW195" s="10"/>
     </row>
-    <row r="196" spans="1:49" ht="14.3" customHeight="1">
+    <row r="196" spans="1:54" ht="14.3" customHeight="1">
       <c r="A196" s="70"/>
       <c r="AW196" s="10"/>
     </row>
-    <row r="197" spans="1:49" ht="14.3" customHeight="1">
+    <row r="197" spans="1:54" ht="14.3" customHeight="1">
       <c r="A197" s="70"/>
       <c r="AW197" s="10"/>
     </row>
-    <row r="198" spans="1:49" ht="14.3" customHeight="1">
+    <row r="198" spans="1:54" ht="14.3" customHeight="1">
       <c r="A198" s="70"/>
       <c r="AW198" s="10"/>
     </row>
-    <row r="199" spans="1:49" ht="14.3" customHeight="1">
+    <row r="199" spans="1:54" ht="14.3" customHeight="1">
       <c r="A199" s="70"/>
       <c r="AW199" s="10"/>
     </row>
-    <row r="200" spans="1:49" ht="14.3" customHeight="1">
+    <row r="200" spans="1:54" ht="14.3" customHeight="1">
       <c r="A200" s="70"/>
       <c r="AW200" s="10"/>
     </row>
-    <row r="201" spans="1:49" ht="14.3" customHeight="1">
+    <row r="201" spans="1:54" ht="14.3" customHeight="1">
       <c r="A201" s="70"/>
       <c r="AW201" s="10"/>
     </row>
-    <row r="202" spans="1:49" ht="14.3" customHeight="1">
+    <row r="202" spans="1:54" ht="14.3" customHeight="1">
       <c r="A202" s="70"/>
       <c r="AW202" s="10"/>
     </row>
-    <row r="203" spans="1:49" ht="14.3" customHeight="1">
+    <row r="203" spans="1:54" ht="14.3" customHeight="1">
       <c r="A203" s="70"/>
       <c r="AW203" s="10"/>
     </row>
-    <row r="204" spans="1:49" ht="14.3" customHeight="1">
+    <row r="204" spans="1:54" ht="14.3" customHeight="1">
       <c r="A204" s="70"/>
       <c r="AW204" s="10"/>
     </row>
-    <row r="205" spans="1:49" ht="14.3" customHeight="1">
+    <row r="205" spans="1:54" ht="14.3" customHeight="1">
       <c r="A205" s="70"/>
       <c r="AW205" s="10"/>
     </row>
-    <row r="206" spans="1:49" ht="14.3" customHeight="1">
+    <row r="206" spans="1:54" ht="14.3" customHeight="1">
       <c r="A206" s="70"/>
       <c r="AW206" s="10"/>
     </row>
-    <row r="207" spans="1:49" ht="14.3" customHeight="1">
+    <row r="207" spans="1:54" ht="14.3" customHeight="1">
       <c r="A207" s="70"/>
       <c r="AW207" s="10"/>
     </row>
-    <row r="208" spans="1:49" ht="14.3" customHeight="1">
+    <row r="208" spans="1:54" ht="14.3" customHeight="1">
       <c r="A208" s="70"/>
       <c r="AW208" s="10"/>
     </row>
@@ -27897,16 +28191,16 @@
     <row r="1018" spans="1:49" ht="14.3" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="Q1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AG1:AJ1"/>
     <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AR1:AU1"/>
     <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E144" r:id="rId1" xr:uid="{A81C656A-0A99-4267-9649-0EEFD2B27222}"/>
@@ -27921,10 +28215,13 @@
     <hyperlink ref="E188" r:id="rId10" tooltip="DOI URL" xr:uid="{71E22F72-0CF3-4154-834D-5AA603563583}"/>
     <hyperlink ref="E189" r:id="rId11" xr:uid="{C96102E8-A232-4FB7-86C2-1DF66DEBB549}"/>
     <hyperlink ref="E190" r:id="rId12" xr:uid="{8048047A-11A2-4914-AA30-CADB42BA1A40}"/>
+    <hyperlink ref="E191" r:id="rId13" display="https://doi.org/10.1016/j.envint.2026.110429" xr:uid="{A8CFEA85-96A6-4EB2-9519-3D355F9DB6A8}"/>
+    <hyperlink ref="E192" r:id="rId14" xr:uid="{50B7E77B-853E-4D24-9D46-277F2F5E3E9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
